--- a/FLR Model.xlsx
+++ b/FLR Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerem\OneDrive\Masaüstü\Financial Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{691C30E9-1CD8-4A14-B8CB-8E7DFA0D336E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD4105E-EB32-48DD-97DC-73ADE7D70FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35796" yWindow="1764" windowWidth="22824" windowHeight="12252" activeTab="1" xr2:uid="{64BEE0EA-45A1-4490-9445-11F5F6D37C44}"/>
+    <workbookView xWindow="30828" yWindow="492" windowWidth="29364" windowHeight="15768" xr2:uid="{64BEE0EA-45A1-4490-9445-11F5F6D37C44}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="7" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="141">
   <si>
     <t>Ticker</t>
   </si>
@@ -279,9 +279,6 @@
     <t>Last Updated</t>
   </si>
   <si>
-    <t>Intelligent Cloud</t>
-  </si>
-  <si>
     <t>Product Segments</t>
   </si>
   <si>
@@ -307,15 +304,6 @@
   </si>
   <si>
     <t>Stock Based Compensation</t>
-  </si>
-  <si>
-    <t>OpenAI</t>
-  </si>
-  <si>
-    <t>Productivity</t>
-  </si>
-  <si>
-    <t>Personal Computing</t>
   </si>
   <si>
     <t>FCF Value</t>
@@ -521,14 +509,14 @@
     <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="167" formatCode="0.00%;\(0.00%\)"/>
-    <numFmt numFmtId="168" formatCode="00\x"/>
-    <numFmt numFmtId="169" formatCode="0.0%;\(0.0%\)"/>
-    <numFmt numFmtId="170" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="171" formatCode="#,##0.0;\(#,##0.0\);\-"/>
-    <numFmt numFmtId="172" formatCode="0.00%;\(0.00%\);\-"/>
-    <numFmt numFmtId="173" formatCode="#,##0;\(#,###\);\-"/>
-    <numFmt numFmtId="174" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.00%;\(0.00%\)"/>
+    <numFmt numFmtId="167" formatCode="00\x"/>
+    <numFmt numFmtId="168" formatCode="0.0%;\(0.0%\)"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0;\(#,##0.0\);\-"/>
+    <numFmt numFmtId="171" formatCode="0.00%;\(0.00%\);\-"/>
+    <numFmt numFmtId="172" formatCode="#,##0;\(#,###\);\-"/>
+    <numFmt numFmtId="173" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
@@ -821,7 +809,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -852,24 +840,24 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="171" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -881,16 +869,20 @@
     <xf numFmtId="37" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -913,10 +905,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1079,62 +1067,6 @@
         </a:extLst>
       </xdr:spPr>
     </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>114301</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1570857" cy="335280"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69627574-06A4-4485-8D53-5683E36A3869}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="670560" y="114301"/>
-          <a:ext cx="1570857" cy="335280"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
@@ -1958,7 +1890,7 @@
     </row>
     <row r="4" spans="1:40" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>53</v>
@@ -2041,29 +1973,29 @@
       <c r="T6" s="18"/>
       <c r="U6" s="6"/>
       <c r="W6" s="15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="X6" s="6"/>
       <c r="Y6" s="6"/>
       <c r="AA6" s="15" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AB6" s="6"/>
       <c r="AC6" s="33" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AD6" s="33" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AF6" s="15" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AG6" s="6"/>
       <c r="AH6" s="33" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AI6" s="33" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:40" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2071,16 +2003,16 @@
         <v>0</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="70">
         <v>22995</v>
       </c>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
       <c r="M7" s="1" t="s">
         <v>46</v>
       </c>
@@ -2095,32 +2027,16 @@
         <v>8.7499999999999994E-2</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="Y7" s="8">
         <f>SUM(J108:N108)+SUM(Y21:AD21)</f>
         <v>0</v>
       </c>
-      <c r="AA7" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC7" s="8" t="e">
-        <f>Segments!#REF!*AD7</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD7" s="34">
-        <v>16</v>
-      </c>
-      <c r="AF7" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH7" s="8" t="e">
-        <f>Segments!#REF!*AI7</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AI7" s="34">
-        <v>30</v>
-      </c>
+      <c r="AC7" s="8"/>
+      <c r="AD7" s="34"/>
+      <c r="AH7" s="8"/>
+      <c r="AI7" s="34"/>
     </row>
     <row r="8" spans="1:40" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
@@ -2130,9 +2046,9 @@
       <c r="G8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="71"/>
+      <c r="K8" s="71"/>
       <c r="M8" s="1" t="s">
         <v>47</v>
       </c>
@@ -2153,26 +2069,10 @@
         <f>AD21*(1+0.035)/($U$7-0.035)</f>
         <v>0</v>
       </c>
-      <c r="AA8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC8" s="8" t="e">
-        <f>Segments!#REF!*AD8</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD8" s="34">
-        <v>22</v>
-      </c>
-      <c r="AF8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH8" s="8" t="e">
-        <f>Segments!#REF!*AI8</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AI8" s="34">
-        <v>40</v>
-      </c>
+      <c r="AC8" s="8"/>
+      <c r="AD8" s="34"/>
+      <c r="AH8" s="8"/>
+      <c r="AI8" s="34"/>
     </row>
     <row r="9" spans="1:40" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
@@ -2185,11 +2085,11 @@
       <c r="G9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I9" s="72" t="s">
-        <v>144</v>
-      </c>
-      <c r="J9" s="72"/>
-      <c r="K9" s="72"/>
+      <c r="I9" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="J9" s="74"/>
+      <c r="K9" s="74"/>
       <c r="M9" s="1" t="s">
         <v>52</v>
       </c>
@@ -2204,26 +2104,10 @@
         <f>P10</f>
         <v>0</v>
       </c>
-      <c r="AA9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC9" s="8" t="e">
-        <f>Segments!#REF!*AD9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD9" s="34">
-        <v>10</v>
-      </c>
-      <c r="AF9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AH9" s="8" t="e">
-        <f>Segments!#REF!*AI9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AI9" s="34">
-        <v>20</v>
-      </c>
+      <c r="AC9" s="8"/>
+      <c r="AD9" s="34"/>
+      <c r="AH9" s="8"/>
+      <c r="AI9" s="34"/>
     </row>
     <row r="10" spans="1:40" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
@@ -2236,11 +2120,11 @@
       <c r="G10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="72">
+      <c r="I10" s="74">
         <v>1912</v>
       </c>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72"/>
+      <c r="J10" s="74"/>
+      <c r="K10" s="74"/>
       <c r="M10" s="1" t="s">
         <v>32</v>
       </c>
@@ -2262,32 +2146,18 @@
         <f>Y7+Y8+Y9</f>
         <v>0</v>
       </c>
-      <c r="AA10" s="6" t="s">
-        <v>77</v>
-      </c>
+      <c r="AA10" s="6"/>
       <c r="AB10" s="6"/>
-      <c r="AC10" s="9">
-        <f>AD10*0.27</f>
-        <v>81000</v>
-      </c>
-      <c r="AD10" s="9">
-        <v>300000</v>
-      </c>
-      <c r="AF10" s="6" t="s">
-        <v>77</v>
-      </c>
+      <c r="AC10" s="9"/>
+      <c r="AD10" s="9"/>
+      <c r="AF10" s="6"/>
       <c r="AG10" s="6"/>
-      <c r="AH10" s="9">
-        <f>AI10*0.25</f>
-        <v>250000</v>
-      </c>
-      <c r="AI10" s="9">
-        <v>1000000</v>
-      </c>
+      <c r="AH10" s="9"/>
+      <c r="AI10" s="9"/>
     </row>
     <row r="11" spans="1:40" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E11" s="14">
         <f ca="1">(K17/E9)^(1/2)-1</f>
@@ -2296,13 +2166,13 @@
       <c r="G11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="72" t="s">
-        <v>143</v>
-      </c>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
+      <c r="I11" s="74" t="s">
+        <v>139</v>
+      </c>
+      <c r="J11" s="74"/>
+      <c r="K11" s="74"/>
       <c r="M11" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P11" s="8">
         <f>500000*0.27</f>
@@ -2311,38 +2181,36 @@
       <c r="R11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="T11" s="70">
-        <v>3012960</v>
-      </c>
-      <c r="U11" s="70"/>
+      <c r="T11" s="72"/>
+      <c r="U11" s="72"/>
       <c r="W11" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Y11" s="19">
         <f>Y10/P12</f>
         <v>0</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC11" s="19" t="e">
+        <v>77</v>
+      </c>
+      <c r="AC11" s="19">
         <f>SUM(AC7:AC10)/$P$12</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD11" s="34">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="34" t="e">
         <f>AVERAGE(AD7:AD9)</f>
-        <v>16</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AF11" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AH11" s="19" t="e">
+        <v>77</v>
+      </c>
+      <c r="AH11" s="19">
         <f>SUM(AH7:AH10)/$P$12</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AI11" s="34">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="34" t="e">
         <f>AVERAGE(AI7:AI9)</f>
-        <v>30</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AM11" s="19"/>
       <c r="AN11" s="34"/>
@@ -2357,11 +2225,11 @@
       <c r="G12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="69">
+      <c r="I12" s="71">
         <v>46387</v>
       </c>
-      <c r="J12" s="69"/>
-      <c r="K12" s="69"/>
+      <c r="J12" s="71"/>
+      <c r="K12" s="71"/>
       <c r="M12" s="1" t="s">
         <v>48</v>
       </c>
@@ -2371,9 +2239,7 @@
       <c r="R12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="U12" s="10">
-        <v>0.98680000000000001</v>
-      </c>
+      <c r="U12" s="10"/>
       <c r="Y12" s="14"/>
       <c r="AC12" s="14"/>
     </row>
@@ -2391,12 +2257,12 @@
       </c>
       <c r="U13" s="10">
         <f>U14+(U15*U17)</f>
-        <v>8.5546000000000011E-2</v>
-      </c>
-      <c r="W13" s="66" t="s">
-        <v>83</v>
-      </c>
-      <c r="X13" s="67"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="68" t="s">
+        <v>79</v>
+      </c>
+      <c r="X13" s="69"/>
       <c r="Y13" s="3">
         <v>2031</v>
       </c>
@@ -2422,22 +2288,20 @@
       </c>
       <c r="AF13" s="6"/>
       <c r="AG13" s="40" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AH13" s="33" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI13" s="33" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:40" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="R14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="U14" s="10">
-        <v>4.0500000000000001E-2</v>
-      </c>
+      <c r="U14" s="10"/>
       <c r="W14" s="1" t="s">
         <v>10</v>
       </c>
@@ -2468,22 +2332,22 @@
       <c r="AF14" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="AG14" s="41" t="e">
+      <c r="AG14" s="41">
         <f>AC11</f>
-        <v>#REF!</v>
+        <v>0</v>
       </c>
       <c r="AH14" s="35">
         <f>E8</f>
         <v>0</v>
       </c>
-      <c r="AI14" s="35" t="e">
+      <c r="AI14" s="35">
         <f>AH11</f>
-        <v>#REF!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:40" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>25</v>
@@ -2516,7 +2380,7 @@
         <v>6</v>
       </c>
       <c r="M15" s="18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N15" s="18"/>
       <c r="O15" s="18"/>
@@ -2524,9 +2388,6 @@
       <c r="R15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="U15" s="1">
-        <v>1.01</v>
-      </c>
       <c r="W15" s="1" t="s">
         <v>11</v>
       </c>
@@ -2555,7 +2416,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AF15" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG15" s="42">
         <v>0.25</v>
@@ -2619,23 +2480,21 @@
       <c r="R17" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="U17" s="10">
-        <v>4.4600000000000001E-2</v>
-      </c>
+      <c r="U17" s="10"/>
       <c r="AF17" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AG17" s="44" t="e">
+        <v>90</v>
+      </c>
+      <c r="AG17" s="44">
         <f>AG14*AG15</f>
-        <v>#REF!</v>
+        <v>0</v>
       </c>
       <c r="AH17" s="39">
         <f>AH14*AH15</f>
         <v>0</v>
       </c>
-      <c r="AI17" s="39" t="e">
+      <c r="AI17" s="39">
         <f>AI14*AI15</f>
-        <v>#REF!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:35" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2659,9 +2518,7 @@
       <c r="R18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="U18" s="8">
-        <v>60590</v>
-      </c>
+      <c r="U18" s="8"/>
       <c r="W18" s="1" t="s">
         <v>23</v>
       </c>
@@ -2692,7 +2549,7 @@
     </row>
     <row r="19" spans="1:35" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M19" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P19" s="25">
         <f ca="1">$P$17/119262</f>
@@ -2701,9 +2558,7 @@
       <c r="R19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="U19" s="10">
-        <v>1.32E-2</v>
-      </c>
+      <c r="U19" s="10"/>
       <c r="W19" s="5" t="s">
         <v>15</v>
       </c>
@@ -2734,9 +2589,9 @@
       <c r="AF19" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AG19" s="39" t="e">
+      <c r="AG19" s="39">
         <f>AG17+AH17+AI17</f>
-        <v>#REF!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:35" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2751,7 +2606,7 @@
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
       <c r="M20" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P20" s="25">
         <f ca="1">$P$17/129705</f>
@@ -2760,15 +2615,13 @@
       <c r="R20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="U20" s="10">
-        <v>4.8500000000000001E-2</v>
-      </c>
+      <c r="U20" s="10"/>
       <c r="AF20" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="AG20" s="14" t="e">
+        <v>91</v>
+      </c>
+      <c r="AG20" s="14">
         <f ca="1">AG19/$E$9-1</f>
-        <v>#REF!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21" spans="1:35" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2783,7 +2636,7 @@
       <c r="J21" s="12"/>
       <c r="K21" s="12"/>
       <c r="M21" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P21" s="25">
         <f ca="1">$P$17/305453</f>
@@ -2792,9 +2645,7 @@
       <c r="R21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="U21" s="10">
-        <v>0.18</v>
-      </c>
+      <c r="U21" s="10"/>
       <c r="W21" s="1" t="s">
         <v>24</v>
       </c>
@@ -2837,7 +2688,7 @@
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
       <c r="M22" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P22" s="25">
         <f ca="1">P18/175259</f>
@@ -2847,11 +2698,8 @@
         <v>43</v>
       </c>
       <c r="S22" s="6"/>
-      <c r="T22" s="71">
-        <f>T11+U18</f>
-        <v>3073550</v>
-      </c>
-      <c r="U22" s="71"/>
+      <c r="T22" s="73"/>
+      <c r="U22" s="73"/>
     </row>
     <row r="23" spans="1:35" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
@@ -2870,12 +2718,12 @@
       </c>
       <c r="U23" s="10">
         <f>(U12*U13)+(U19*U20*(1-U21))</f>
-        <v>8.4941756800000018E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:35" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>4</v>
@@ -3193,7 +3041,7 @@
     </row>
     <row r="48" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E48" s="48"/>
       <c r="F48" s="48"/>
@@ -3226,7 +3074,7 @@
     </row>
     <row r="51" spans="1:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
@@ -3256,7 +3104,7 @@
     </row>
     <row r="54" spans="1:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3408,7 +3256,7 @@
     </row>
     <row r="62" spans="1:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E62" s="11"/>
       <c r="F62" s="11"/>
@@ -3485,7 +3333,7 @@
     </row>
     <row r="68" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="12"/>
@@ -3529,7 +3377,7 @@
     </row>
     <row r="71" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E71" s="48"/>
       <c r="F71" s="48"/>
@@ -3571,7 +3419,7 @@
     </row>
     <row r="74" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E74" s="48"/>
       <c r="F74" s="48"/>
@@ -3601,7 +3449,7 @@
     </row>
     <row r="77" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
@@ -3631,7 +3479,7 @@
     </row>
     <row r="80" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>21</v>
@@ -3932,7 +3780,7 @@
     </row>
     <row r="102" spans="1:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E102" s="13"/>
       <c r="F102" s="13"/>
@@ -3964,7 +3812,7 @@
     </row>
     <row r="105" spans="1:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E105" s="12"/>
       <c r="F105" s="12"/>
@@ -4006,10 +3854,10 @@
     </row>
     <row r="110" spans="1:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
@@ -4060,7 +3908,7 @@
     </row>
     <row r="112" spans="1:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E112" s="47">
         <f t="shared" ref="E112:N112" si="3">E51/E118</f>
@@ -4105,7 +3953,7 @@
     </row>
     <row r="113" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E113" s="45"/>
       <c r="F113" s="45" t="e">
@@ -4147,7 +3995,7 @@
     </row>
     <row r="115" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E115" s="47" t="e">
         <f t="shared" ref="E115:N115" si="5">E51/E121</f>
@@ -4192,7 +4040,7 @@
     </row>
     <row r="116" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E116" s="45"/>
       <c r="F116" s="45" t="e">
@@ -4273,7 +4121,7 @@
     </row>
     <row r="119" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E119" s="45"/>
       <c r="F119" s="45">
@@ -4328,7 +4176,7 @@
     </row>
     <row r="121" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B121" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E121" s="28">
         <f t="shared" ref="E121:K121" si="8">E18</f>
@@ -4373,7 +4221,7 @@
     </row>
     <row r="122" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B122" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E122" s="45"/>
       <c r="F122" s="45" t="e">
@@ -4415,7 +4263,7 @@
     </row>
     <row r="124" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B124" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E124" s="50" t="e">
         <f>E17/E112</f>
@@ -4460,7 +4308,7 @@
     </row>
     <row r="125" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B125" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E125" s="51" t="e">
         <f>E17/(E42/E121)</f>
@@ -4505,7 +4353,7 @@
     </row>
     <row r="126" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E126" s="51" t="e">
         <f>E17/((E42+E56)/E121)</f>
@@ -4550,7 +4398,7 @@
     </row>
     <row r="127" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B127" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E127" s="51" t="e">
         <f>E17/(E27/E121)</f>
@@ -4595,7 +4443,7 @@
     </row>
     <row r="128" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B128" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E128" s="51" t="e">
         <f>E17/(E105/E121)</f>
@@ -4671,7 +4519,7 @@
   <sheetData>
     <row r="2" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>50</v>
@@ -4679,10 +4527,10 @@
     </row>
     <row r="4" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="54"/>
@@ -4746,7 +4594,7 @@
       </c>
       <c r="D6" s="59"/>
       <c r="E6" s="59">
-        <f t="shared" ref="D6:E6" si="0">SUM(E9,E13,E17,E21)</f>
+        <f t="shared" ref="E6" si="0">SUM(E9,E13,E17,E21)</f>
         <v>14156</v>
       </c>
       <c r="F6" s="59">
@@ -4782,7 +4630,7 @@
       </c>
       <c r="E7" s="58"/>
       <c r="F7" s="58">
-        <f t="shared" ref="E7:L7" si="1">(F6-E6)/E6</f>
+        <f t="shared" ref="F7:L7" si="1">(F6-E6)/E6</f>
         <v>-2.9104266742017521E-2</v>
       </c>
       <c r="G7" s="58">
@@ -4818,7 +4666,7 @@
     </row>
     <row r="9" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D9" s="60"/>
       <c r="E9" s="60">
@@ -4853,38 +4701,38 @@
     </row>
     <row r="10" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D10" s="58"/>
-      <c r="E10" s="74">
-        <f t="shared" ref="D10:L10" si="2">E9/E$6</f>
+      <c r="E10" s="67">
+        <f t="shared" ref="E10:L10" si="2">E9/E$6</f>
         <v>0.35009889799378358</v>
       </c>
-      <c r="F10" s="74">
+      <c r="F10" s="67">
         <f t="shared" si="2"/>
         <v>0.42724097788125726</v>
       </c>
-      <c r="G10" s="74">
+      <c r="G10" s="67">
         <f t="shared" si="2"/>
         <v>0.40758691999483004</v>
       </c>
-      <c r="H10" s="74">
+      <c r="H10" s="67">
         <f t="shared" si="2"/>
         <v>0.36628869138829301</v>
       </c>
-      <c r="I10" s="74">
+      <c r="I10" s="67">
         <f t="shared" si="2"/>
         <v>0.2292459523963104</v>
       </c>
-      <c r="J10" s="74">
+      <c r="J10" s="67">
         <f t="shared" si="2"/>
         <v>0.21323147074117035</v>
       </c>
-      <c r="K10" s="74">
+      <c r="K10" s="67">
         <f t="shared" si="2"/>
         <v>0.23032832169798931</v>
       </c>
-      <c r="L10" s="74">
+      <c r="L10" s="67">
         <f t="shared" si="2"/>
         <v>0.25525508851848216</v>
       </c>
@@ -4894,32 +4742,32 @@
       <c r="B11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74">
-        <f t="shared" ref="E11:K11" si="3">(F9-E9)/E9</f>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67">
+        <f t="shared" ref="F11:K11" si="3">(F9-E9)/E9</f>
         <v>0.1848264729620662</v>
       </c>
-      <c r="G11" s="74">
+      <c r="G11" s="67">
         <f t="shared" si="3"/>
         <v>7.408038147138965E-2</v>
       </c>
-      <c r="H11" s="74">
+      <c r="H11" s="67">
         <f t="shared" si="3"/>
         <v>-5.2481369906453149E-2</v>
       </c>
-      <c r="I11" s="74">
+      <c r="I11" s="67">
         <f t="shared" si="3"/>
         <v>-0.40528781793842034</v>
       </c>
-      <c r="J11" s="74">
+      <c r="J11" s="67">
         <f t="shared" si="3"/>
         <v>-4.0000000000000084E-2</v>
       </c>
-      <c r="K11" s="74">
+      <c r="K11" s="67">
         <f t="shared" si="3"/>
         <v>0.17999999999999997</v>
       </c>
-      <c r="L11" s="74">
+      <c r="L11" s="67">
         <f t="shared" ref="L11" si="4">(L9-K9)/K9</f>
         <v>0.19999999999999987</v>
       </c>
@@ -4931,7 +4779,7 @@
     </row>
     <row r="13" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D13" s="60"/>
       <c r="E13" s="60">
@@ -4969,37 +4817,37 @@
     </row>
     <row r="14" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E14" s="74">
-        <f t="shared" ref="D14:L14" si="5">E13/E$6</f>
+        <v>131</v>
+      </c>
+      <c r="E14" s="67">
+        <f t="shared" ref="E14:L14" si="5">E13/E$6</f>
         <v>0.31195252896298387</v>
       </c>
-      <c r="F14" s="74">
+      <c r="F14" s="67">
         <f t="shared" si="5"/>
         <v>0.28528812572759021</v>
       </c>
-      <c r="G14" s="74">
+      <c r="G14" s="67">
         <f t="shared" si="5"/>
         <v>0.34005428460643661</v>
       </c>
-      <c r="H14" s="74">
+      <c r="H14" s="67">
         <f t="shared" si="5"/>
         <v>0.44370211461844927</v>
       </c>
-      <c r="I14" s="74">
+      <c r="I14" s="67">
         <f t="shared" si="5"/>
         <v>0.59343352899438817</v>
       </c>
-      <c r="J14" s="74">
+      <c r="J14" s="67">
         <f t="shared" si="5"/>
         <v>0.63247470101195957</v>
       </c>
-      <c r="K14" s="74">
+      <c r="K14" s="67">
         <f t="shared" si="5"/>
         <v>0.62528922830604061</v>
       </c>
-      <c r="L14" s="74">
+      <c r="L14" s="67">
         <f t="shared" si="5"/>
         <v>0.60633978542560207</v>
       </c>
@@ -5010,32 +4858,32 @@
       <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74">
-        <f t="shared" ref="E15:K15" si="6">(F13-E13)/E13</f>
+      <c r="E15" s="67"/>
+      <c r="F15" s="67">
+        <f t="shared" ref="F15:K15" si="6">(F13-E13)/E13</f>
         <v>-0.11209239130434782</v>
       </c>
-      <c r="G15" s="74">
+      <c r="G15" s="67">
         <f t="shared" si="6"/>
         <v>0.34200459066564654</v>
       </c>
-      <c r="H15" s="74">
+      <c r="H15" s="67">
         <f t="shared" si="6"/>
         <v>0.37571265678449262</v>
       </c>
-      <c r="I15" s="74">
+      <c r="I15" s="67">
         <f t="shared" si="6"/>
         <v>0.27089376985771513</v>
       </c>
-      <c r="J15" s="74">
+      <c r="J15" s="67">
         <f t="shared" si="6"/>
         <v>0.1</v>
       </c>
-      <c r="K15" s="74">
+      <c r="K15" s="67">
         <f t="shared" si="6"/>
         <v>8.0000000000000029E-2</v>
       </c>
-      <c r="L15" s="74">
+      <c r="L15" s="67">
         <f t="shared" ref="L15" si="7">(L13-K13)/K13</f>
         <v>5.0000000000000128E-2</v>
       </c>
@@ -5048,7 +4896,7 @@
     </row>
     <row r="17" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D17" s="60"/>
       <c r="E17" s="60">
@@ -5083,37 +4931,37 @@
     </row>
     <row r="18" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E18" s="74">
-        <f t="shared" ref="D18:L18" si="8">E17/E$6</f>
+        <v>131</v>
+      </c>
+      <c r="E18" s="67">
+        <f t="shared" ref="E18:L18" si="8">E17/E$6</f>
         <v>0.2163746821135914</v>
       </c>
-      <c r="F18" s="74">
+      <c r="F18" s="67">
         <f t="shared" si="8"/>
         <v>0.16654540162980211</v>
       </c>
-      <c r="G18" s="74">
+      <c r="G18" s="67">
         <f t="shared" si="8"/>
         <v>0.17157813105854983</v>
       </c>
-      <c r="H18" s="74">
+      <c r="H18" s="67">
         <f t="shared" si="8"/>
         <v>0.15899479007048728</v>
       </c>
-      <c r="I18" s="74">
+      <c r="I18" s="67">
         <f t="shared" si="8"/>
         <v>0.17544991292008</v>
       </c>
-      <c r="J18" s="74">
+      <c r="J18" s="67">
         <f t="shared" si="8"/>
         <v>0.15299388024479021</v>
       </c>
-      <c r="K18" s="74">
+      <c r="K18" s="67">
         <f t="shared" si="8"/>
         <v>0.14355289595827084</v>
       </c>
-      <c r="L18" s="74">
+      <c r="L18" s="67">
         <f t="shared" si="8"/>
         <v>0.13787677509859786</v>
       </c>
@@ -5124,39 +4972,39 @@
       <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74">
-        <f t="shared" ref="E19:K19" si="9">(F17-E17)/E17</f>
+      <c r="E19" s="67"/>
+      <c r="F19" s="67">
+        <f t="shared" ref="F19:K19" si="9">(F17-E17)/E17</f>
         <v>-0.25269343780607245</v>
       </c>
-      <c r="G19" s="74">
+      <c r="G19" s="67">
         <f t="shared" si="9"/>
         <v>0.15989515072083879</v>
       </c>
-      <c r="H19" s="74">
+      <c r="H19" s="67">
         <f t="shared" si="9"/>
         <v>-2.2975517890772127E-2</v>
       </c>
-      <c r="I19" s="74">
+      <c r="I19" s="67">
         <f t="shared" si="9"/>
         <v>4.8573631457208943E-2</v>
       </c>
-      <c r="J19" s="74">
+      <c r="J19" s="67">
         <f t="shared" si="9"/>
         <v>-0.1</v>
       </c>
-      <c r="K19" s="74">
+      <c r="K19" s="67">
         <f t="shared" si="9"/>
         <v>2.4999999999999925E-2</v>
       </c>
-      <c r="L19" s="74">
+      <c r="L19" s="67">
         <f t="shared" ref="L19" si="10">(L17-K17)/K17</f>
         <v>3.999999999999998E-2</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D21" s="60"/>
       <c r="E21" s="60">
@@ -5186,44 +5034,44 @@
     </row>
     <row r="22" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="56" t="s">
-        <v>135</v>
-      </c>
-      <c r="E22" s="74"/>
-      <c r="F22" s="74">
-        <f t="shared" ref="D22:L22" si="11">F21/F$6</f>
+        <v>131</v>
+      </c>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67">
+        <f t="shared" ref="F22:L22" si="11">F21/F$6</f>
         <v>0.12092549476135041</v>
       </c>
-      <c r="G22" s="74">
+      <c r="G22" s="67">
         <f t="shared" si="11"/>
         <v>8.0780664340183536E-2</v>
       </c>
-      <c r="H22" s="74">
+      <c r="H22" s="67">
         <f t="shared" si="11"/>
         <v>3.1014403922770457E-2</v>
       </c>
-      <c r="I22" s="74">
+      <c r="I22" s="67">
         <f t="shared" si="11"/>
         <v>1.870605689221441E-3</v>
       </c>
-      <c r="J22" s="74">
+      <c r="J22" s="67">
         <f t="shared" si="11"/>
         <v>1.299948002079917E-3</v>
       </c>
-      <c r="K22" s="74">
+      <c r="K22" s="67">
         <f t="shared" si="11"/>
         <v>8.2955403769923775E-4</v>
       </c>
-      <c r="L22" s="74">
+      <c r="L22" s="67">
         <f t="shared" si="11"/>
         <v>5.2835095731783147E-4</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="54"/>
@@ -5285,7 +5133,7 @@
       </c>
       <c r="D26" s="59"/>
       <c r="E26" s="59">
-        <f t="shared" ref="D26:I26" si="12">SUM(E29,E33,E37,E41)</f>
+        <f t="shared" ref="E26:I26" si="12">SUM(E29,E33,E37,E41)</f>
         <v>9970</v>
       </c>
       <c r="F26" s="59">
@@ -5319,7 +5167,7 @@
       </c>
       <c r="E27" s="58"/>
       <c r="F27" s="58">
-        <f t="shared" ref="E27:K27" si="13">(F26-E26)/E26</f>
+        <f t="shared" ref="F27:K27" si="13">(F26-E26)/E26</f>
         <v>0.98746238716148449</v>
       </c>
       <c r="G27" s="58">
@@ -5345,7 +5193,7 @@
     </row>
     <row r="29" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D29" s="60"/>
       <c r="E29" s="60">
@@ -5372,11 +5220,11 @@
     </row>
     <row r="30" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D30" s="58"/>
       <c r="E30" s="58">
-        <f t="shared" ref="D30:K30" si="14">E29/E$26</f>
+        <f t="shared" ref="E30:K30" si="14">E29/E$26</f>
         <v>0.33229689067201607</v>
       </c>
       <c r="F30" s="58">
@@ -5410,7 +5258,7 @@
       </c>
       <c r="E31" s="58"/>
       <c r="F31" s="58">
-        <f t="shared" ref="E31:K31" si="15">(F29-E29)/E29</f>
+        <f t="shared" ref="F31:K31" si="15">(F29-E29)/E29</f>
         <v>0.96528825837609422</v>
       </c>
       <c r="G31" s="58">
@@ -5436,7 +5284,7 @@
     </row>
     <row r="33" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D33" s="60"/>
       <c r="E33" s="60">
@@ -5463,10 +5311,10 @@
     </row>
     <row r="34" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E34" s="58">
-        <f t="shared" ref="D34:K34" si="16">E33/E$26</f>
+        <f t="shared" ref="E34:K34" si="16">E33/E$26</f>
         <v>0.27291875626880641</v>
       </c>
       <c r="F34" s="58">
@@ -5500,7 +5348,7 @@
       </c>
       <c r="E35" s="58"/>
       <c r="F35" s="58">
-        <f t="shared" ref="E35:K35" si="17">(F33-E33)/E33</f>
+        <f t="shared" ref="F35:K35" si="17">(F33-E33)/E33</f>
         <v>1.4987137081955164</v>
       </c>
       <c r="G35" s="58">
@@ -5526,7 +5374,7 @@
     </row>
     <row r="37" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D37" s="60"/>
       <c r="E37" s="60">
@@ -5553,10 +5401,10 @@
     </row>
     <row r="38" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E38" s="58">
-        <f t="shared" ref="D38:K38" si="18">E37/E$26</f>
+        <f t="shared" ref="E38:K38" si="18">E37/E$26</f>
         <v>0.27261785356068202</v>
       </c>
       <c r="F38" s="58">
@@ -5590,7 +5438,7 @@
       </c>
       <c r="E39" s="58"/>
       <c r="F39" s="58">
-        <f t="shared" ref="E39:K39" si="19">(F37-E37)/E37</f>
+        <f t="shared" ref="F39:K39" si="19">(F37-E37)/E37</f>
         <v>0.9672553348050037</v>
       </c>
       <c r="G39" s="58">
@@ -5616,7 +5464,7 @@
     </row>
     <row r="41" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D41" s="60"/>
       <c r="E41" s="60">
@@ -5643,10 +5491,10 @@
     </row>
     <row r="42" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="56" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E42" s="58">
-        <f t="shared" ref="D42:K42" si="20">E41/E$26</f>
+        <f t="shared" ref="E42:K42" si="20">E41/E$26</f>
         <v>0.12216649949849549</v>
       </c>
       <c r="F42" s="58">
@@ -5676,10 +5524,10 @@
     </row>
     <row r="44" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="54"/>
@@ -5741,7 +5589,7 @@
       </c>
       <c r="D46" s="59"/>
       <c r="E46" s="59">
-        <f t="shared" ref="D46:I46" si="21">SUM(E49,E53,E57,E61)</f>
+        <f t="shared" ref="E46:I46" si="21">SUM(E49,E53,E57,E61)</f>
         <v>20800</v>
       </c>
       <c r="F46" s="59">
@@ -5775,7 +5623,7 @@
       </c>
       <c r="E47" s="58"/>
       <c r="F47" s="58">
-        <f t="shared" ref="E47:K47" si="22">(F46-E46)/E46</f>
+        <f t="shared" ref="F47:K47" si="22">(F46-E46)/E46</f>
         <v>0.25235576923076924</v>
       </c>
       <c r="G47" s="58">
@@ -5801,7 +5649,7 @@
     </row>
     <row r="49" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D49" s="60"/>
       <c r="E49" s="60">
@@ -5828,11 +5676,11 @@
     </row>
     <row r="50" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D50" s="58"/>
       <c r="E50" s="58">
-        <f t="shared" ref="D50:K50" si="23">E49/E$46</f>
+        <f t="shared" ref="E50:K50" si="23">E49/E$46</f>
         <v>0.44826923076923075</v>
       </c>
       <c r="F50" s="58">
@@ -5866,7 +5714,7 @@
       </c>
       <c r="E51" s="58"/>
       <c r="F51" s="58">
-        <f t="shared" ref="E51:K51" si="24">(F49-E49)/E49</f>
+        <f t="shared" ref="F51:K51" si="24">(F49-E49)/E49</f>
         <v>-2.0377520377520379E-2</v>
       </c>
       <c r="G51" s="58">
@@ -5892,7 +5740,7 @@
     </row>
     <row r="53" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D53" s="60"/>
       <c r="E53" s="60">
@@ -5919,10 +5767,10 @@
     </row>
     <row r="54" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E54" s="58">
-        <f t="shared" ref="D54:K54" si="25">E53/E$46</f>
+        <f t="shared" ref="E54:K54" si="25">E53/E$46</f>
         <v>0.33884615384615385</v>
       </c>
       <c r="F54" s="58">
@@ -5956,7 +5804,7 @@
       </c>
       <c r="E55" s="58"/>
       <c r="F55" s="58">
-        <f t="shared" ref="E55:K55" si="26">(F53-E53)/E53</f>
+        <f t="shared" ref="F55:K55" si="26">(F53-E53)/E53</f>
         <v>0.40465380249716232</v>
       </c>
       <c r="G55" s="58">
@@ -5982,7 +5830,7 @@
     </row>
     <row r="57" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D57" s="60"/>
       <c r="E57" s="60">
@@ -6009,10 +5857,10 @@
     </row>
     <row r="58" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E58" s="58">
-        <f t="shared" ref="D58:K58" si="27">E57/E$46</f>
+        <f t="shared" ref="E58:K58" si="27">E57/E$46</f>
         <v>0.12317307692307693</v>
       </c>
       <c r="F58" s="58">
@@ -6046,7 +5894,7 @@
       </c>
       <c r="E59" s="58"/>
       <c r="F59" s="58">
-        <f t="shared" ref="E59:K59" si="28">(F57-E57)/E57</f>
+        <f t="shared" ref="F59:K59" si="28">(F57-E57)/E57</f>
         <v>1.2115534738485558</v>
       </c>
       <c r="G59" s="58">
@@ -6072,7 +5920,7 @@
     </row>
     <row r="61" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D61" s="60"/>
       <c r="E61" s="60">
@@ -6099,10 +5947,10 @@
     </row>
     <row r="62" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="56" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E62" s="58">
-        <f t="shared" ref="D62:K62" si="29">E61/E$46</f>
+        <f t="shared" ref="E62:K62" si="29">E61/E$46</f>
         <v>8.9711538461538468E-2</v>
       </c>
       <c r="F62" s="58">
@@ -6132,10 +5980,10 @@
     </row>
     <row r="64" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="54"/>
@@ -6231,7 +6079,7 @@
       </c>
       <c r="D67" s="58"/>
       <c r="E67" s="58">
-        <f t="shared" ref="D67:I67" si="30">E66/E6</f>
+        <f t="shared" ref="E67:I67" si="30">E66/E6</f>
         <v>-1.9285108787793163E-2</v>
       </c>
       <c r="F67" s="58">
@@ -6265,7 +6113,7 @@
     </row>
     <row r="69" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D69" s="64"/>
       <c r="E69" s="64">
@@ -6302,7 +6150,7 @@
       </c>
       <c r="D70" s="58"/>
       <c r="E70" s="58">
-        <f t="shared" ref="D70:I70" si="31">E69/E9</f>
+        <f t="shared" ref="E70:I70" si="31">E69/E9</f>
         <v>5.0443906376109765E-2</v>
       </c>
       <c r="F70" s="58">
@@ -6346,7 +6194,7 @@
     </row>
     <row r="72" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D72" s="64"/>
       <c r="E72" s="64">
@@ -6429,7 +6277,7 @@
     </row>
     <row r="75" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D75" s="64"/>
       <c r="E75" s="64">
@@ -6509,7 +6357,7 @@
     </row>
     <row r="78" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D78" s="64"/>
       <c r="E78" s="64">
@@ -6540,7 +6388,7 @@
       </c>
       <c r="D79" s="58"/>
       <c r="E79" s="58">
-        <f t="shared" ref="D79:I79" si="34">E78/E21</f>
+        <f t="shared" ref="E79:I79" si="34">E78/E21</f>
         <v>-0.15862870424171993</v>
       </c>
       <c r="F79" s="58">
@@ -6570,7 +6418,7 @@
     </row>
     <row r="81" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="55" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D81" s="57"/>
       <c r="E81" s="57"/>
@@ -6633,68 +6481,68 @@
   <sheetData>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="H2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="N2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="S2" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="H3" s="72" t="s">
-        <v>112</v>
-      </c>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72" t="s">
-        <v>113</v>
-      </c>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
-      <c r="O3" s="72"/>
-      <c r="P3" s="72" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="72"/>
-      <c r="S3" s="72"/>
+      <c r="H3" s="74" t="s">
+        <v>108</v>
+      </c>
+      <c r="I3" s="74"/>
+      <c r="J3" s="74"/>
+      <c r="K3" s="74"/>
+      <c r="L3" s="74" t="s">
+        <v>109</v>
+      </c>
+      <c r="M3" s="74"/>
+      <c r="N3" s="74"/>
+      <c r="O3" s="74"/>
+      <c r="P3" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q3" s="74"/>
+      <c r="R3" s="74"/>
+      <c r="S3" s="74"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -6702,40 +6550,40 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="26" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="K4" s="26" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="L4" s="26" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="M4" s="26" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="Q4" s="26" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="R4" s="26" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="S4" s="26" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:19" s="21" customFormat="1" ht="1.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6843,7 +6691,7 @@
       <c r="G3" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="H3" s="73" cm="1">
+      <c r="H3" s="66" cm="1">
         <f t="array" aca="1" ref="H3" ca="1">_FV(G3,"Price")</f>
         <v>52.99</v>
       </c>
